--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA257"/>
+  <dimension ref="A1:AA258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29013,6 +29013,111 @@
       <c r="Z257" s="2" t="inlineStr"/>
       <c r="AA257" s="2" t="inlineStr"/>
     </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>21636</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Hermanus</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Overberg District Municipality</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>1 Hemel en Aarde Road</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>jpr@winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>+27 28 316 3988</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr"/>
+      <c r="R258" s="2" t="inlineStr"/>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winevillagehermanus/</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winevillagehermanus</t>
+        </is>
+      </c>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr"/>
+      <c r="W258" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Pierre Rossouw</t>
+        </is>
+      </c>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jprossouw</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA258"/>
+  <dimension ref="A1:AA260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29118,6 +29118,200 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Wine Tonight?</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Wine Tonight?</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>122639</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>1 Dreyer Street</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>7708</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winetonight.co.za</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>jess@winetonight.co.za</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 492 5393</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr"/>
+      <c r="R259" s="2" t="inlineStr"/>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winetonightcavendishsquare</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winetonightcavendish/</t>
+        </is>
+      </c>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr"/>
+      <c r="W259" s="2" t="inlineStr"/>
+      <c r="X259" s="2" t="inlineStr"/>
+      <c r="Y259" s="2" t="inlineStr"/>
+      <c r="Z259" s="2" t="inlineStr"/>
+      <c r="AA259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>21636</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Hermanus</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Overberg District Municipality</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>1 Hemel en Aarde Road</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>jpr@winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>+27 28 316 3988</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr"/>
+      <c r="R260" s="2" t="inlineStr"/>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winevillagehermanus/</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winevillagehermanus</t>
+        </is>
+      </c>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Pierre Rossouw</t>
+        </is>
+      </c>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr"/>
+      <c r="AA260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jprossouw</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29312,6 +29312,301 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Oasis Liquor Wholesalers Cc</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Oasis Liquor Wholesalers Cc</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>121897</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>57 End Street</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>https://oasisliquordistributors.co.za</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>sales@oasisliquor.co.za</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 402 7165</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>199701136723</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oasis-liquor-distributors/</t>
+        </is>
+      </c>
+      <c r="S261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/OasisLiquorDistributors</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oasisliquordistributors</t>
+        </is>
+      </c>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr"/>
+      <c r="X261" s="2" t="inlineStr"/>
+      <c r="Y261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Wine Tonight?</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Wine Tonight?</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>122639</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>1 Dreyer Street</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>7708</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winetonight.co.za</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>jess@winetonight.co.za</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 492 5393</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr"/>
+      <c r="R262" s="2" t="inlineStr"/>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winetonightcavendishsquare</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winetonightcavendish/</t>
+        </is>
+      </c>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr"/>
+      <c r="W262" s="2" t="inlineStr"/>
+      <c r="X262" s="2" t="inlineStr"/>
+      <c r="Y262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr"/>
+      <c r="AA262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Wine Village Hermanus Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>21636</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Hermanus</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Overberg District Municipality</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>1 Hemel en Aarde Road</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>jpr@winevillage.co.za</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>+27 28 316 3988</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr"/>
+      <c r="R263" s="2" t="inlineStr"/>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winevillagehermanus/</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winevillagehermanus</t>
+        </is>
+      </c>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t>Jean-Pierre Rossouw</t>
+        </is>
+      </c>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr"/>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jprossouw</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA263"/>
+  <dimension ref="A1:AA265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29607,6 +29607,216 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Wheels</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Wheels</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>22248</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga, Ehlanzeni District Municipality</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>7 Alie Van Bergen Street</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>https://wineonwheels.co.za</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>orders@wineonwheels.co.za</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>+27 13 751 2242</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
+          <t>200208498023</t>
+        </is>
+      </c>
+      <c r="R264" s="2" t="inlineStr"/>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineOnWheels/</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineonwheelslowveld/</t>
+        </is>
+      </c>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr">
+        <is>
+          <t>Neil Liston</t>
+        </is>
+      </c>
+      <c r="X264" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y264" s="2" t="inlineStr"/>
+      <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neil-liston-7181a42/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Wheels</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Wheels</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>22248</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga, Ehlanzeni District Municipality</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>7 Alie Van Bergen Street</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>https://wineonwheels.co.za</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>orders@wineonwheels.co.za</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>+27 13 751 2242</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>200208498023</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr"/>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineOnWheels/</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineonwheelslowveld/</t>
+        </is>
+      </c>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr"/>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>Kim Liston</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kim-liston-994b9b13/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA265"/>
+  <dimension ref="A1:AA271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -29817,6 +29817,624 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Navigate World Whisky (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Navigate World Whisky (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>122072</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Midrand</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Postnet Suite #235, Private Bag X11, Halfway House</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>https://spiritssouthafrica.co.za, https://www.navigateworldwhisky.com</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr"/>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>info@navigateworldwhisky.com</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 466 4660</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr"/>
+      <c r="Q266" s="2" t="inlineStr"/>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/navigate-world-whisky/</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/NavigateWorldWhisky</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/NavigateWorldWhisky</t>
+        </is>
+      </c>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@navigateworldwhisky5855/</t>
+        </is>
+      </c>
+      <c r="W266" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa Adendorff</t>
+        </is>
+      </c>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanessa-adendorff-43b89715b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Constantiaberg Business Park</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr"/>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>Fernando P. Rueda</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Director</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-rueda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Constantiaberg Business Park</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr"/>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>Johan Rossouw</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-rossouw-737b65b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Wines Of The World Distributors Pty. Ltd.</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Wines Of The World Distributors Pty. Ltd.</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>122069</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>14 Viljoen Street</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>https://wineoftheworld.co.za</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>admin@wineoftheworld.co.za</t>
+        </is>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 624 3363</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>196700401507</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr"/>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100054389535335</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winesoftheworlddistributors/</t>
+        </is>
+      </c>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr"/>
+      <c r="W269" s="2" t="inlineStr"/>
+      <c r="X269" s="2" t="inlineStr"/>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Pb Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Pb Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>29053</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands District Municipality</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Bottelary Road</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>7605</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pbliquor.co.za</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>info@pbliquor.co.za</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 020 1600</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>200603036807</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr"/>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/PB-Liquor-Merchants-Pty-Ltd-100093520525302</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pb_liquor_merchants/</t>
+        </is>
+      </c>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr">
+        <is>
+          <t>Megan Vendel</t>
+        </is>
+      </c>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Pb Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Pb Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>29053</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands District Municipality</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Bottelary Road</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>7605</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pbliquor.co.za</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>info@pbliquor.co.za</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 020 1600</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>200603036807</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr"/>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/PB-Liquor-Merchants-Pty-Ltd-100093520525302</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pb_liquor_merchants/</t>
+        </is>
+      </c>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>Chris Morkel</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-morkel-923920a2/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA271"/>
+  <dimension ref="A1:AA272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30435,6 +30435,103 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Deeliver</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Deeliver</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>84510</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Donkerhoek</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Tshwane Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Plot 48</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://copperwines.co.za, https://www.deeliver.co.za</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>hello@deeliver.co.za</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 238 2212</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr"/>
+      <c r="Q272" s="2" t="inlineStr"/>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deeliver/</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr"/>
+      <c r="T272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/DeeliverZA</t>
+        </is>
+      </c>
+      <c r="V272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@deeliver</t>
+        </is>
+      </c>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>Jason D.</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasondelbridge/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA272"/>
+  <dimension ref="A1:AA275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30532,6 +30532,297 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>47262</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Jeffreys Bay</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape, Western District</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>Blaaukrans Street</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>sales@frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>+27 42 293 1806</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>199904871623</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr"/>
+      <c r="S273" s="2" t="inlineStr"/>
+      <c r="T273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>Fraser Schenck</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>47262</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Jeffreys Bay</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape, Western District</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Blaaukrans Street</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>sales@frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>+27 42 293 1806</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>199904871623</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr"/>
+      <c r="S274" s="2" t="inlineStr"/>
+      <c r="T274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>Brad Smith</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Frasafrica Marketing Cc</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>47262</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Jeffreys Bay</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape, Western District</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Blaaukrans Street</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>sales@frasafrica.co.za</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>+27 42 293 1806</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>199904871623</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr"/>
+      <c r="S275" s="2" t="inlineStr"/>
+      <c r="T275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>Mark Doyle</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr"/>
+      <c r="Z275" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA275" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA275"/>
+  <dimension ref="A1:AA277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30823,6 +30823,208 @@
       </c>
       <c r="AA275" s="2" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="inlineStr"/>
+      <c r="T276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
+          <t>Ludolph Hough</t>
+        </is>
+      </c>
+      <c r="X276" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ludolph-hough-48768422a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S277" s="2" t="inlineStr"/>
+      <c r="T277" s="2" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>Jason Cederwall</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-cederwall-9789a2118/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA277"/>
+  <dimension ref="A1:AA279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31025,6 +31025,208 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>Ludolph Hough</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="AA278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ludolph-hough-48768422a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S279" s="2" t="inlineStr"/>
+      <c r="T279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr"/>
+      <c r="W279" s="2" t="inlineStr">
+        <is>
+          <t>Jason Cederwall</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-cederwall-9789a2118/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA279"/>
+  <dimension ref="A1:AA289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -31227,6 +31227,1044 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr"/>
+      <c r="T280" s="2" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>Sinegugu Miya</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>Junior Trade Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sinegugu-miya-2b71ab220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S281" s="2" t="inlineStr"/>
+      <c r="T281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>Jason Cederwall</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-cederwall-9789a2118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr"/>
+      <c r="T282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr">
+        <is>
+          <t>Marinda G.</t>
+        </is>
+      </c>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marinda-g-378134a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr"/>
+      <c r="T283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr">
+        <is>
+          <t>Ludolph Hough</t>
+        </is>
+      </c>
+      <c r="X283" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ludolph-hough-48768422a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O284" s="2" t="inlineStr"/>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="inlineStr"/>
+      <c r="W284" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Steenkamp</t>
+        </is>
+      </c>
+      <c r="X284" s="2" t="inlineStr">
+        <is>
+          <t>Brokerage and Auction Manager / Sales</t>
+        </is>
+      </c>
+      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danielle-steenkamp-6161672a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O285" s="2" t="inlineStr"/>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr">
+        <is>
+          <t>Agrinnette Gqokoma</t>
+        </is>
+      </c>
+      <c r="X285" s="2" t="inlineStr">
+        <is>
+          <t>Cellar Manager</t>
+        </is>
+      </c>
+      <c r="Y285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr"/>
+      <c r="AA285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agrinnette-gqokoma-a9592a277/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr"/>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr">
+        <is>
+          <t>Fernando P. Rueda</t>
+        </is>
+      </c>
+      <c r="X286" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="Y286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-rueda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr"/>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr">
+        <is>
+          <t>Johan Rossouw</t>
+        </is>
+      </c>
+      <c r="X287" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr"/>
+      <c r="AA287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-rossouw-737b65b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O288" s="2" t="inlineStr"/>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr">
+        <is>
+          <t>Sanchia Foster-Sutherland</t>
+        </is>
+      </c>
+      <c r="X288" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y288" s="2" t="inlineStr"/>
+      <c r="Z288" s="2" t="inlineStr"/>
+      <c r="AA288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanchia-foster-sutherland-50473179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O289" s="2" t="inlineStr"/>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr">
+        <is>
+          <t>Richard Mugwambani</t>
+        </is>
+      </c>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr"/>
+      <c r="Z289" s="2" t="inlineStr"/>
+      <c r="AA289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-mugwambani-73a0682b9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA289"/>
+  <dimension ref="A1:AA299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32265,6 +32265,1044 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S290" s="2" t="inlineStr"/>
+      <c r="T290" s="2" t="inlineStr"/>
+      <c r="U290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="inlineStr"/>
+      <c r="W290" s="2" t="inlineStr">
+        <is>
+          <t>Sinegugu Miya</t>
+        </is>
+      </c>
+      <c r="X290" s="2" t="inlineStr">
+        <is>
+          <t>Junior Trade Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr"/>
+      <c r="AA290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sinegugu-miya-2b71ab220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr"/>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr"/>
+      <c r="T291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="inlineStr"/>
+      <c r="W291" s="2" t="inlineStr">
+        <is>
+          <t>Jason Cederwall</t>
+        </is>
+      </c>
+      <c r="X291" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr"/>
+      <c r="AA291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-cederwall-9789a2118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr"/>
+      <c r="T292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>Marinda G.</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marinda-g-378134a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr"/>
+      <c r="T293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>Ludolph Hough</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ludolph-hough-48768422a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr"/>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Steenkamp</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>Brokerage and Auction Manager / Sales</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danielle-steenkamp-6161672a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr"/>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>Agrinnette Gqokoma</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>Cellar Manager</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr"/>
+      <c r="AA295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agrinnette-gqokoma-a9592a277/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr"/>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>Fernando P. Rueda</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-rueda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr"/>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr"/>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>Johan Rossouw</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-rossouw-737b65b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr"/>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>Sanchia Foster-Sutherland</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanchia-foster-sutherland-50473179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr"/>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>Richard Mugwambani</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-mugwambani-73a0682b9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA299"/>
+  <dimension ref="A1:AA309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -33303,6 +33303,1044 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr"/>
+      <c r="T300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr">
+        <is>
+          <t>Sinegugu Miya</t>
+        </is>
+      </c>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>Junior Trade Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sinegugu-miya-2b71ab220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr"/>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr"/>
+      <c r="T301" s="2" t="inlineStr"/>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr">
+        <is>
+          <t>Jason Cederwall</t>
+        </is>
+      </c>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-cederwall-9789a2118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr"/>
+      <c r="T302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>Marinda G.</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marinda-g-378134a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Craft Liquor Merchants (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>49664</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>17 Spartan Crescent</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clmbrands.com</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr"/>
+      <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@clmbrands.com</t>
+        </is>
+      </c>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>+27 87 405 4434</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>201724415707</t>
+        </is>
+      </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/craft-liquor-merchants/</t>
+        </is>
+      </c>
+      <c r="S303" s="2" t="inlineStr"/>
+      <c r="T303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="inlineStr"/>
+      <c r="V303" s="2" t="inlineStr"/>
+      <c r="W303" s="2" t="inlineStr">
+        <is>
+          <t>Ludolph Hough</t>
+        </is>
+      </c>
+      <c r="X303" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ludolph-hough-48768422a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M304" s="2" t="inlineStr"/>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O304" s="2" t="inlineStr"/>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="inlineStr"/>
+      <c r="W304" s="2" t="inlineStr">
+        <is>
+          <t>Danielle Steenkamp</t>
+        </is>
+      </c>
+      <c r="X304" s="2" t="inlineStr">
+        <is>
+          <t>Brokerage and Auction Manager / Sales</t>
+        </is>
+      </c>
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danielle-steenkamp-6161672a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr"/>
+      <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr"/>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr"/>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="inlineStr"/>
+      <c r="W305" s="2" t="inlineStr">
+        <is>
+          <t>Agrinnette Gqokoma</t>
+        </is>
+      </c>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>Cellar Manager</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agrinnette-gqokoma-a9592a277/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr"/>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr"/>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U306" s="2" t="inlineStr"/>
+      <c r="V306" s="2" t="inlineStr"/>
+      <c r="W306" s="2" t="inlineStr">
+        <is>
+          <t>Fernando P. Rueda</t>
+        </is>
+      </c>
+      <c r="X306" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="Y306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fernando-rueda/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr"/>
+      <c r="K307" s="2" t="inlineStr"/>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr"/>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O307" s="2" t="inlineStr"/>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U307" s="2" t="inlineStr"/>
+      <c r="V307" s="2" t="inlineStr"/>
+      <c r="W307" s="2" t="inlineStr">
+        <is>
+          <t>Johan Rossouw</t>
+        </is>
+      </c>
+      <c r="X307" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="Y307" s="2" t="inlineStr"/>
+      <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johan-rossouw-737b65b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr"/>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O308" s="2" t="inlineStr"/>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U308" s="2" t="inlineStr"/>
+      <c r="V308" s="2" t="inlineStr"/>
+      <c r="W308" s="2" t="inlineStr">
+        <is>
+          <t>Sanchia Foster-Sutherland</t>
+        </is>
+      </c>
+      <c r="X308" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanchia-foster-sutherland-50473179/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Rueda Wine Consulting (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>122071</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Unit 50, Constantiaberg Business Park, Diep River</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>https://ruedawine.com</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr"/>
+      <c r="K309" s="2" t="inlineStr"/>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr"/>
+      <c r="N309" s="2" t="inlineStr">
+        <is>
+          <t>info@ruedawine.com</t>
+        </is>
+      </c>
+      <c r="O309" s="2" t="inlineStr"/>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
+          <t>202085052607</t>
+        </is>
+      </c>
+      <c r="R309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rueda-wine/</t>
+        </is>
+      </c>
+      <c r="S309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Ruedawine</t>
+        </is>
+      </c>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruedawine/</t>
+        </is>
+      </c>
+      <c r="U309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="inlineStr"/>
+      <c r="W309" s="2" t="inlineStr">
+        <is>
+          <t>Richard Mugwambani</t>
+        </is>
+      </c>
+      <c r="X309" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-mugwambani-73a0682b9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
